--- a/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
+++ b/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
+++ b/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
+++ b/zaini_case_audit_output/outputs/excel/09_case_brief_register.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
